--- a/data_out/country_spreadsheets/Italy.xlsx
+++ b/data_out/country_spreadsheets/Italy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W108"/>
+  <dimension ref="A1:AN108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>62.58</v>
       </c>
+      <c r="X2" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>134.83</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>257.66</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>62.58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>40.97</v>
       </c>
+      <c r="X3" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>145.67</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>108.56</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>106.73</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>221.43</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>226.15</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>119.89</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>222.29</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>111.39</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>40.97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>0.2</v>
       </c>
+      <c r="X4" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>193.95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>184.32</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>90.41</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>115.59</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>258.66</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>273.33</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>107.43</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>120.85</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>162.62</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>257.36</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>109.17</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>20.85</v>
       </c>
+      <c r="X5" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>88.31</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>134.87</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>121.56</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>10.31</v>
       </c>
+      <c r="X6" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>247.24</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>306.03</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>263.01</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>274.38</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>136.64</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10.31</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>88.98</v>
       </c>
+      <c r="X7" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>164</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>130.91</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>241.78</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>176.04</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>88.98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>181.81</v>
       </c>
+      <c r="X8" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>136.94</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>140.04</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>182.88</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>276.84</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>192.19</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>56.74</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>181.81</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>147.58</v>
       </c>
+      <c r="X9" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>189.33</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>252.23</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>246.43</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>167.47</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>93.17</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>147.58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>42.4</v>
       </c>
+      <c r="X10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>132.58</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>42.4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>10.37</v>
       </c>
+      <c r="X11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>165.54</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>166.56</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75.18000000000001</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>309.42</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>236.3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10.37</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>60.92</v>
       </c>
+      <c r="X12" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>105.04</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>79.58</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>191.51</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>259.34</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60.92</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>21.72</v>
       </c>
+      <c r="X13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>147.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>121.08</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>122.43</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>278.47</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>220.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>21.72</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>1.74</v>
       </c>
+      <c r="X14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>108.12</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>236.99</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>220.14</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>100.48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.74</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>3.98</v>
       </c>
+      <c r="X15" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>151.87</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>95.70999999999999</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>199.62</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>224.28</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>214.19</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>238.71</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>298.93</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>134.03</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>3.98</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>9.35</v>
       </c>
+      <c r="X16" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>161.65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>179.63</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>157.67</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>213.69</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>270.14</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>110.94</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.35</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>48.35</v>
       </c>
+      <c r="X17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>211.78</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>129.52</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>129.95</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>217.97</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>143.97</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>200.83</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>281.73</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>127.84</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>138.21</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48.35</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>12.97</v>
       </c>
+      <c r="X18" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>150.99</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>152.24</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>198.92</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>12.97</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>0.52</v>
       </c>
+      <c r="X19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>173.14</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>106.54</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>65.03</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>212.85</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>194.59</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>134.68</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>2.61</v>
       </c>
+      <c r="X20" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>37.01</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>159.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>146.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>156.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>265.49</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>103.26</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>197.95</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.61</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>76.59</v>
       </c>
+      <c r="X21" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>151.26</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>173.98</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>305.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>93.70999999999999</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>93.56999999999999</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>262.06</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>151.54</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>76.59</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>12.68</v>
       </c>
+      <c r="X22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>66.27</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>188.86</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>262.13</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>48.36</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>273.65</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>287.67</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>115.39</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>12.68</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>4.89</v>
       </c>
+      <c r="X23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>155.57</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>232.37</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>244.93</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>63.86</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>4.89</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>8.199999999999999</v>
       </c>
+      <c r="X24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>50.59</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>167.95</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>117.81</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>285.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>175.05</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>8.199999999999999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>13.16</v>
       </c>
+      <c r="X25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>159.73</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>210.19</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>281.88</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>135.79</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>216.76</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>282.68</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>261.94</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13.16</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>5.37</v>
       </c>
+      <c r="X26" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>151.73</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>110.99</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>52.06</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>183.57</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>253.43</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>152.63</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>5.37</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>4.02</v>
       </c>
+      <c r="X27" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>126.04</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>143.24</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>4.02</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>15.51</v>
       </c>
+      <c r="X28" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>178.47</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>165.89</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>75.53</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>152.51</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>203.48</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>140.93</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>219.47</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15.51</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2700,6 +4162,57 @@
       <c r="W29" t="n">
         <v>24.05</v>
       </c>
+      <c r="X29" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>140.53</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>77.72</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>142.16</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>125.68</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>319.14</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>295.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>152.35</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>76.93000000000001</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>24.05</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2777,6 +4290,57 @@
       <c r="W30" t="n">
         <v>51.76</v>
       </c>
+      <c r="X30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>163.11</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>108.11</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>133.35</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>247.61</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>199.41</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>131.04</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>210.61</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>51.76</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2854,6 +4418,57 @@
       <c r="W31" t="n">
         <v>5.45</v>
       </c>
+      <c r="X31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>83.06</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>5.45</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2931,6 +4546,57 @@
       <c r="W32" t="n">
         <v>191.77</v>
       </c>
+      <c r="X32" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>138.49</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>114.67</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>131.14</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>191.77</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3008,6 +4674,57 @@
       <c r="W33" t="n">
         <v>17.37</v>
       </c>
+      <c r="X33" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>117.86</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>72.11</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>17.37</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3085,6 +4802,57 @@
       <c r="W34" t="n">
         <v>26.16</v>
       </c>
+      <c r="X34" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>135.23</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>26.16</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3162,6 +4930,57 @@
       <c r="W35" t="n">
         <v>80.81999999999999</v>
       </c>
+      <c r="X35" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>149.68</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>126.87</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>76.73</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>80.81999999999999</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3239,6 +5058,57 @@
       <c r="W36" t="n">
         <v>50.69</v>
       </c>
+      <c r="X36" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>189.05</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>68.81999999999999</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>193.83</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>131.54</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>161.13</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>50.69</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3316,6 +5186,57 @@
       <c r="W37" t="n">
         <v>51.35</v>
       </c>
+      <c r="X37" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>179.18</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>103.66</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>227.79</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>76.58</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>98.11</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>166.77</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>51.35</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -3393,6 +5314,57 @@
       <c r="W38" t="n">
         <v>95.3</v>
       </c>
+      <c r="X38" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>68.63</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>175.33</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>196.71</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>131.12</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>202.54</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>98.17</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>95.3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -3470,6 +5442,57 @@
       <c r="W39" t="n">
         <v>126.13</v>
       </c>
+      <c r="X39" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>102.56</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>156.69</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>202.38</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>157.53</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>143.45</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>64.53</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>137.55</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>276.33</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>126.13</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -3547,6 +5570,57 @@
       <c r="W40" t="n">
         <v>170.28</v>
       </c>
+      <c r="X40" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>95.56</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>118.23</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>199.88</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>272.63</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>170.28</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -3624,6 +5698,57 @@
       <c r="W41" t="n">
         <v>189.92</v>
       </c>
+      <c r="X41" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>212.67</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>269.45</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>189.92</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -3701,6 +5826,57 @@
       <c r="W42" t="n">
         <v>106.29</v>
       </c>
+      <c r="X42" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>209.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>173.19</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>293.61</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>209.72</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>118.28</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>142.12</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>344.92</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>106.29</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -3778,6 +5954,57 @@
       <c r="W43" t="n">
         <v>91.55</v>
       </c>
+      <c r="X43" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>213.85</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>192.48</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>121.18</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>207.86</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>89</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>119.26</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>307.21</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>91.55</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3855,6 +6082,57 @@
       <c r="W44" t="n">
         <v>53.11</v>
       </c>
+      <c r="X44" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>168.86</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>240.95</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>64.83</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>118.43</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>264.54</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>53.11</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3932,6 +6210,57 @@
       <c r="W45" t="n">
         <v>168.37</v>
       </c>
+      <c r="X45" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>96.68000000000001</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>202.34</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>111.03</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>241.27</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>145.08</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>69.97</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>126.59</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>230.12</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>348.92</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>168.37</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -4009,6 +6338,57 @@
       <c r="W46" t="n">
         <v>157.21</v>
       </c>
+      <c r="X46" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>190.87</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>86.29000000000001</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>257.46</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>207.37</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>150.2</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>157.21</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -4086,6 +6466,57 @@
       <c r="W47" t="n">
         <v>118.23</v>
       </c>
+      <c r="X47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>149.72</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>223.51</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>69.06</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>75.89</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>131.31</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>118.23</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -4163,6 +6594,57 @@
       <c r="W48" t="n">
         <v>70.19</v>
       </c>
+      <c r="X48" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>98.68000000000001</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>177.32</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>109.46</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>133.35</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>93.95999999999999</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>70.19</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -4240,6 +6722,57 @@
       <c r="W49" t="n">
         <v>121.51</v>
       </c>
+      <c r="X49" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>95.27</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>148.97</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>174.32</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>73.94</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>102.17</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>129.32</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>121.51</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -4317,6 +6850,57 @@
       <c r="W50" t="n">
         <v>108.46</v>
       </c>
+      <c r="X50" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>155.93</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>103.13</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>150.83</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>134.73</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>239.12</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>108.46</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -4394,6 +6978,57 @@
       <c r="W51" t="n">
         <v>14.41</v>
       </c>
+      <c r="X51" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>152.11</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>177.67</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>151.29</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>273.26</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>282.67</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>14.41</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -4471,6 +7106,57 @@
       <c r="W52" t="n">
         <v>28.85</v>
       </c>
+      <c r="X52" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>96.73999999999999</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>204.92</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>108.79</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>271.7</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>28.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -4548,6 +7234,57 @@
       <c r="W53" t="n">
         <v>31.6</v>
       </c>
+      <c r="X53" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>157.45</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>118.81</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>154.38</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>224.54</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -4625,6 +7362,57 @@
       <c r="W54" t="n">
         <v>49.16</v>
       </c>
+      <c r="X54" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>174.07</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>170.96</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>179.19</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>108.29</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>284.57</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>49.16</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -4702,6 +7490,57 @@
       <c r="W55" t="n">
         <v>127.46</v>
       </c>
+      <c r="X55" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>110.67</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>116.43</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>37.47</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>67.72</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>110.51</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>295.64</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>127.46</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -4779,6 +7618,57 @@
       <c r="W56" t="n">
         <v>100.81</v>
       </c>
+      <c r="X56" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>124.57</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>112.46</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>255.73</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>302.71</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>100.81</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -4856,6 +7746,57 @@
       <c r="W57" t="n">
         <v>78.48999999999999</v>
       </c>
+      <c r="X57" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>106.16</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>156.67</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>202.75</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>180.71</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>172.99</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>114.87</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>312.66</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>78.48999999999999</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -4933,6 +7874,57 @@
       <c r="W58" t="n">
         <v>66.65000000000001</v>
       </c>
+      <c r="X58" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>82.17</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>68.94</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>115.09</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>266.12</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>311.58</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>66.65000000000001</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -5010,6 +8002,57 @@
       <c r="W59" t="n">
         <v>23.57</v>
       </c>
+      <c r="X59" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>151.97</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>221.38</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>193.35</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>94.37</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>143.18</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>293.12</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>23.57</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -5087,6 +8130,57 @@
       <c r="W60" t="n">
         <v>121.17</v>
       </c>
+      <c r="X60" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>111.87</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>110.23</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>259.05</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>178.74</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>133.37</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>215.75</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>121.17</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -5164,6 +8258,57 @@
       <c r="W61" t="n">
         <v>40.87</v>
       </c>
+      <c r="X61" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>70.77</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>148.67</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>118.32</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>109.59</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>173.86</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>109.82</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>195.27</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>243.36</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>292.13</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>40.87</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -5241,6 +8386,57 @@
       <c r="W62" t="n">
         <v>72.53</v>
       </c>
+      <c r="X62" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>62</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>130.29</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>74.20999999999999</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>214.16</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>113.98</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>105.72</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>310.76</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>72.53</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -5318,6 +8514,57 @@
       <c r="W63" t="n">
         <v>149.47</v>
       </c>
+      <c r="X63" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>74.93000000000001</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>170.62</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>220.57</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>157.34</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>133.81</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>305.03</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>149.47</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -5395,6 +8642,57 @@
       <c r="W64" t="n">
         <v>75.44</v>
       </c>
+      <c r="X64" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>181.79</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>156.38</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>78.76000000000001</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>69.39</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>187.75</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>300.04</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>75.44</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -5472,6 +8770,57 @@
       <c r="W65" t="n">
         <v>11.58</v>
       </c>
+      <c r="X65" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>133.97</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>11.58</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -5549,6 +8898,57 @@
       <c r="W66" t="n">
         <v>4.63</v>
       </c>
+      <c r="X66" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>147.36</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>152.81</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>176.46</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>164.95</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>132.96</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>4.63</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -5626,6 +9026,57 @@
       <c r="W67" t="n">
         <v>2.36</v>
       </c>
+      <c r="X67" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>252.99</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>136.96</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>211.88</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>322.29</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>126.07</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>179.27</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>2.36</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -5703,6 +9154,57 @@
       <c r="W68" t="n">
         <v>2.59</v>
       </c>
+      <c r="X68" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>185.51</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>204.07</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>201.39</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>160.59</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>2.59</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -5780,6 +9282,57 @@
       <c r="W69" t="n">
         <v>4.83</v>
       </c>
+      <c r="X69" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>108.81</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>171.72</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>122.12</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>190.32</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>103.13</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>98.06999999999999</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>4.83</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -5857,6 +9410,57 @@
       <c r="W70" t="n">
         <v>17.02</v>
       </c>
+      <c r="X70" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>244.81</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>125.16</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>131.22</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>111.93</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>110.87</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>280.02</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>17.02</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -5934,6 +9538,57 @@
       <c r="W71" t="n">
         <v>8.08</v>
       </c>
+      <c r="X71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>306.43</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>201.02</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>8.08</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -6011,6 +9666,57 @@
       <c r="W72" t="n">
         <v>3.97</v>
       </c>
+      <c r="X72" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>249.94</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>229.13</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>3.97</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -6088,6 +9794,57 @@
       <c r="W73" t="n">
         <v>18.06</v>
       </c>
+      <c r="X73" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>256.53</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>136.16</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>239.98</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>170.22</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>18.06</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -6165,6 +9922,57 @@
       <c r="W74" t="n">
         <v>2.57</v>
       </c>
+      <c r="X74" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>151.61</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>156.12</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>190.21</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>154.63</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>154.87</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>317</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>2.57</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -6242,6 +10050,57 @@
       <c r="W75" t="n">
         <v>18.21</v>
       </c>
+      <c r="X75" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>157.39</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>116.09</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>115.23</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>97.76000000000001</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>131.52</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>79.95999999999999</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>238.49</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>18.21</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -6319,6 +10178,57 @@
       <c r="W76" t="n">
         <v>22</v>
       </c>
+      <c r="X76" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>242.62</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>87.56999999999999</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>114.91</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>187.78</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>126.85</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>265.79</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -6396,6 +10306,57 @@
       <c r="W77" t="n">
         <v>32.5</v>
       </c>
+      <c r="X77" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>67.47</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>275.82</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>188.67</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>118.09</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>141.34</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>65.78</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>226.37</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>32.5</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -6473,6 +10434,57 @@
       <c r="W78" t="n">
         <v>47.1</v>
       </c>
+      <c r="X78" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>199.01</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>154.31</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>339.93</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>116.91</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>275.66</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>182.73</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>47.1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -6550,6 +10562,57 @@
       <c r="W79" t="n">
         <v>40.68</v>
       </c>
+      <c r="X79" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>183.48</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>203.55</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>325.32</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>96.91</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>97.03</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>285.98</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>40.68</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -6627,6 +10690,57 @@
       <c r="W80" t="n">
         <v>24.37</v>
       </c>
+      <c r="X80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>100.87</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>110.63</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>241.75</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>117.78</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>38.82</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>24.37</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -6704,6 +10818,57 @@
       <c r="W81" t="n">
         <v>28.45</v>
       </c>
+      <c r="X81" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>180.01</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>192.75</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>216.21</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>49</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>28.45</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -6781,6 +10946,57 @@
       <c r="W82" t="n">
         <v>32.87</v>
       </c>
+      <c r="X82" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>230.93</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>123.36</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>115.44</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>182.83</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>106.99</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>32.87</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -6858,6 +11074,57 @@
       <c r="W83" t="n">
         <v>43.91</v>
       </c>
+      <c r="X83" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>241.24</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>196.47</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>225.93</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>43.91</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -6935,6 +11202,57 @@
       <c r="W84" t="n">
         <v>4.56</v>
       </c>
+      <c r="X84" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>236.12</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>118.13</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>174.79</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>200.94</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>86.93000000000001</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>87.37</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>4.56</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -7012,6 +11330,57 @@
       <c r="W85" t="n">
         <v>10.42</v>
       </c>
+      <c r="X85" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>218.17</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>127.74</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>191.21</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>275.26</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>148.64</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>157.29</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>10.42</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -7089,6 +11458,57 @@
       <c r="W86" t="n">
         <v>32.05</v>
       </c>
+      <c r="X86" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>195.15</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>182.55</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>78.61</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>142.97</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>192.89</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>259.64</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>132.54</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>208.12</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>32.05</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -7166,6 +11586,57 @@
       <c r="W87" t="n">
         <v>18.43</v>
       </c>
+      <c r="X87" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>140.44</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>275.93</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>103.74</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>18.43</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -7243,6 +11714,57 @@
       <c r="W88" t="n">
         <v>5.97</v>
       </c>
+      <c r="X88" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>146.59</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>138.13</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>232.58</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>5.97</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -7320,6 +11842,57 @@
       <c r="W89" t="n">
         <v>9.9</v>
       </c>
+      <c r="X89" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>146.24</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>160.11</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>60.07</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>154.1</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -7397,6 +11970,57 @@
       <c r="W90" t="n">
         <v>7.59</v>
       </c>
+      <c r="X90" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>177.02</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>122.92</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>137.03</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>107.91</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>127.48</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>246.65</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>70.26000000000001</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>7.59</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -7474,6 +12098,57 @@
       <c r="W91" t="n">
         <v>7.24</v>
       </c>
+      <c r="X91" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>164.65</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>163.73</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>101.78</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>98.37</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>153.78</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>155.59</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>7.24</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -7551,6 +12226,57 @@
       <c r="W92" t="n">
         <v>0.53</v>
       </c>
+      <c r="X92" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>231.34</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>80.02</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>205.22</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>198.19</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>73.03</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -7628,6 +12354,57 @@
       <c r="W93" t="n">
         <v>0.6</v>
       </c>
+      <c r="X93" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>269.62</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>193.95</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>113.33</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>135.07</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>246.66</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -7705,6 +12482,57 @@
       <c r="W94" t="n">
         <v>19.04</v>
       </c>
+      <c r="X94" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>149.49</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>174.84</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>269.35</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>172.74</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>137.34</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>19.04</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -7782,6 +12610,57 @@
       <c r="W95" t="n">
         <v>29.89</v>
       </c>
+      <c r="X95" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>217.09</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>183.21</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>139.51</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>67.78</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>141.15</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>211.91</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>113.53</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>29.89</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -7859,6 +12738,57 @@
       <c r="W96" t="n">
         <v>0.15</v>
       </c>
+      <c r="X96" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>267.09</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>192.42</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>308.49</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>118.72</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>122.51</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>124.82</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -7936,6 +12866,57 @@
       <c r="W97" t="n">
         <v>31.43</v>
       </c>
+      <c r="X97" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>204.36</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>152.45</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>142.76</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>31.43</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -8013,6 +12994,57 @@
       <c r="W98" t="n">
         <v>14.01</v>
       </c>
+      <c r="X98" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>287.11</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>232.23</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>127.09</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>144.88</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>14.01</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -8090,6 +13122,57 @@
       <c r="W99" t="n">
         <v>42.52</v>
       </c>
+      <c r="X99" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>200.72</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>186.67</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>131.63</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>166.26</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>142.51</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>120.02</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>80.81</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>231.48</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>42.52</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -8167,6 +13250,57 @@
       <c r="W100" t="n">
         <v>27.74</v>
       </c>
+      <c r="X100" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>271.34</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>178.39</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>75.98</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>67.53</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>128.28</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>104.82</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>27.74</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -8244,6 +13378,57 @@
       <c r="W101" t="n">
         <v>16.18</v>
       </c>
+      <c r="X101" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>255.68</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>91.87</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>105.51</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>112.91</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>125.06</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>16.18</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -8321,6 +13506,57 @@
       <c r="W102" t="n">
         <v>22.93</v>
       </c>
+      <c r="X102" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>222.13</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>129.12</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>124.54</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>167.09</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>22.93</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -8398,6 +13634,57 @@
       <c r="W103" t="n">
         <v>10.56</v>
       </c>
+      <c r="X103" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>299.17</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>150.8</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>82.13</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>134.11</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>105.56</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>10.56</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -8475,6 +13762,57 @@
       <c r="W104" t="n">
         <v>0.86</v>
       </c>
+      <c r="X104" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>278.84</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>217.1</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>73.06999999999999</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -8552,6 +13890,57 @@
       <c r="W105" t="n">
         <v>0.36</v>
       </c>
+      <c r="X105" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>230.17</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>180.08</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -8629,6 +14018,57 @@
       <c r="W106" t="n">
         <v>66.86</v>
       </c>
+      <c r="X106" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>152.55</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>172.16</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>182.99</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>130.12</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>66.86</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -8706,6 +14146,57 @@
       <c r="W107" t="n">
         <v>43.1</v>
       </c>
+      <c r="X107" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>183.28</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>118.22</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>43.1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -8781,6 +14272,57 @@
         <v>30.17</v>
       </c>
       <c r="W108" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="X108" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>124.08</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>168.54</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>79.95999999999999</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="AN108" t="n">
         <v>25.59</v>
       </c>
     </row>
